--- a/algorithm/output_result/return_metrics/icici nav_Return_Metrics.xlsx
+++ b/algorithm/output_result/return_metrics/icici nav_Return_Metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,17 +495,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.71</v>
+        <v>0.09</v>
       </c>
       <c r="E2" t="n">
-        <v>3.84</v>
+        <v>3.73</v>
       </c>
       <c r="F2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>1.94</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.53</v>
+      </c>
       <c r="H2" t="n">
-        <v>2.89</v>
+        <v>2.0725</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -513,13 +515,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>70.37</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="3">
@@ -539,17 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.36</v>
+        <v>0.34</v>
       </c>
       <c r="E3" t="n">
-        <v>2.95</v>
+        <v>3.43</v>
       </c>
       <c r="F3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>1.79</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.11</v>
+      </c>
       <c r="H3" t="n">
-        <v>2.29</v>
+        <v>2.4175</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -557,13 +561,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>66.67</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="4">
@@ -583,19 +587,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="E4" t="n">
-        <v>1.34</v>
+        <v>2.81</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.84</v>
+        <v>-2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.73</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4724999999999999</v>
+        <v>0.8875</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -603,13 +607,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L4" t="n">
-        <v>22.22</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="5">
@@ -629,17 +633,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.19</v>
+        <v>0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="F5" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+        <v>2.28</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.98</v>
+      </c>
       <c r="H5" t="n">
-        <v>3.136666666666667</v>
+        <v>2.6875</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -647,13 +653,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L5" t="n">
-        <v>74.06999999999999</v>
+        <v>54.17</v>
       </c>
     </row>
     <row r="6">
@@ -673,17 +679,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.36</v>
+        <v>0.76</v>
       </c>
       <c r="E6" t="n">
-        <v>2.98</v>
+        <v>3.88</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>2.16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.52</v>
+      </c>
       <c r="H6" t="n">
-        <v>2.28</v>
+        <v>2.83</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -694,10 +702,10 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L6" t="n">
-        <v>62.96</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="7">
@@ -717,19 +725,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3</v>
+        <v>2.77</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.92</v>
+        <v>-2.52</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.83</v>
+        <v>1.22</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5325</v>
+        <v>0.8425</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -737,13 +745,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
-        <v>18.52</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8">
@@ -763,17 +771,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.74</v>
+        <v>0.71</v>
       </c>
       <c r="E8" t="n">
-        <v>1.69</v>
+        <v>2.78</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+        <v>0.06</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.55</v>
+      </c>
       <c r="H8" t="n">
-        <v>1.243333333333333</v>
+        <v>1.525</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -781,13 +791,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>37.04</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -807,19 +817,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.62</v>
+        <v>2.36</v>
       </c>
       <c r="E9" t="n">
-        <v>3.63</v>
+        <v>5.35</v>
       </c>
       <c r="F9" t="n">
-        <v>0.15</v>
+        <v>2.34</v>
       </c>
       <c r="G9" t="n">
-        <v>1.52</v>
+        <v>3.78</v>
       </c>
       <c r="H9" t="n">
-        <v>1.73</v>
+        <v>3.4575</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -827,13 +837,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L9" t="n">
-        <v>55.56</v>
+        <v>70.83</v>
       </c>
     </row>
     <row r="10">
@@ -853,17 +863,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.59</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>4.16</v>
+        <v>4.04</v>
       </c>
       <c r="F10" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>7.14</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.17</v>
+      </c>
       <c r="H10" t="n">
-        <v>4.37</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -871,13 +883,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L10" t="n">
-        <v>85.19</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="11">
@@ -897,17 +909,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.26</v>
+        <v>0.28</v>
       </c>
       <c r="E11" t="n">
-        <v>2.25</v>
+        <v>2.94</v>
       </c>
       <c r="F11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+        <v>0.22</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.92</v>
+      </c>
       <c r="H11" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -915,13 +929,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>40.74</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="12">
@@ -941,19 +955,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02</v>
+        <v>1.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.47</v>
+        <v>-3.94</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.68</v>
+        <v>-0.58</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.845</v>
+        <v>-0.255</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -961,13 +975,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>11.11</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="13">
@@ -987,17 +1001,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.84</v>
+        <v>2.53</v>
       </c>
       <c r="E13" t="n">
-        <v>1.23</v>
+        <v>4.42</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>-0.48</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.05</v>
+      </c>
       <c r="H13" t="n">
-        <v>0.5333333333333334</v>
+        <v>2.63</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1005,13 +1021,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L13" t="n">
-        <v>25.93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1031,17 +1047,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.95</v>
+        <v>0.53</v>
       </c>
       <c r="E14" t="n">
-        <v>5.45</v>
+        <v>4.66</v>
       </c>
       <c r="F14" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
+        <v>8.859999999999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10.26</v>
+      </c>
       <c r="H14" t="n">
-        <v>5.606666666666666</v>
+        <v>6.077500000000001</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1049,13 +1067,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L14" t="n">
-        <v>92.59</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1066,26 +1084,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mid Cap Index Fund</t>
+          <t>Mid Cap 150 Momentum 50 Index Fund</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ULIF 149 050723 McIndxFund 105</t>
+          <t>ULIF 151 180124 McMomentum 105</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.78</v>
+        <v>-0.35</v>
       </c>
       <c r="E15" t="n">
-        <v>4.07</v>
+        <v>2.95</v>
       </c>
       <c r="F15" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
+        <v>4.09</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.63</v>
+      </c>
       <c r="H15" t="n">
-        <v>4.453333333333333</v>
+        <v>2.08</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1093,13 +1113,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L15" t="n">
-        <v>88.89</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="16">
@@ -1110,28 +1130,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mid Cap 150 Momentum 50 Index Fund</t>
+          <t>Multicap 50 25 25 Index Fund</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ULIF 151 180124 McMomentum 105</t>
+          <t>ULIF 152 220224 MultiCapIF 105</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-3.02</v>
+        <v>1.79</v>
       </c>
       <c r="E16" t="n">
-        <v>0.67</v>
+        <v>4.21</v>
       </c>
       <c r="F16" t="n">
-        <v>1.28</v>
+        <v>4.09</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.53</v>
+        <v>3.07</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.65</v>
+        <v>3.29</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1139,13 +1159,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L16" t="n">
-        <v>14.81</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="17">
@@ -1156,28 +1176,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Multicap 50 25 25 Index Fund</t>
+          <t>MidSmall Cap 400 Index Fund</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ULIF 152 220224 MultiCapIF 105</t>
+          <t>ULIF 153 150424 MidSmal400 105</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="E17" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="F17" t="n">
-        <v>1.64</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2</v>
+        <v>6.21</v>
       </c>
       <c r="H17" t="n">
-        <v>1.55</v>
+        <v>5.685</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1185,13 +1205,13 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L17" t="n">
-        <v>48.15</v>
+        <v>95.83</v>
       </c>
     </row>
     <row r="18">
@@ -1202,28 +1222,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MidSmall Cap 400 Index Fund</t>
+          <t>Pension India Growth Fund</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ULIF 153 150424 MidSmal400 105</t>
+          <t>ULIF 154 260624 PenIndGrwt 105</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>0.82</v>
       </c>
       <c r="E18" t="n">
-        <v>5.83</v>
+        <v>3.8</v>
       </c>
       <c r="F18" t="n">
-        <v>6.44</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.05</v>
+        <v>4.85</v>
       </c>
       <c r="H18" t="n">
-        <v>3.955</v>
+        <v>2.6275</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1231,13 +1251,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L18" t="n">
-        <v>81.48</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="19">
@@ -1248,26 +1268,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pension India Growth Fund</t>
+          <t>MidSmallCap 400 Momentum Quality 100 Index Fund</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ULIF 154 260624 PenIndGrwt 105</t>
+          <t>ULIF 156 251024 MscMomQual 105</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.51</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="F19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+        <v>8.35</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.54</v>
+      </c>
       <c r="H19" t="n">
-        <v>1.823333333333333</v>
+        <v>3.98</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1275,13 +1297,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L19" t="n">
-        <v>59.26</v>
+        <v>79.17</v>
       </c>
     </row>
     <row r="20">
@@ -1292,28 +1314,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MidSmallCap 400 Momentum Quality 100 Index Fund</t>
+          <t>Smallcap250 Momentum Quality 100 Index Fund</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ULIF 156 251024 MscMomQual 105</t>
+          <t>ULIF 157 301224 SmcMomQual 105</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.92</v>
+        <v>1.18</v>
       </c>
       <c r="E20" t="n">
-        <v>1.56</v>
+        <v>6.37</v>
       </c>
       <c r="F20" t="n">
-        <v>6.33</v>
+        <v>10.74</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.96</v>
+        <v>1.58</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0025</v>
+        <v>4.967499999999999</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1321,13 +1343,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L20" t="n">
-        <v>33.33</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="21">
@@ -1338,28 +1360,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Smallcap250 Momentum Quality 100 Index Fund</t>
+          <t>India Consumption Fund</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ULIF 157 301224 SmcMomQual 105</t>
+          <t>ULIF 158 170425 IndConsump 105</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="E21" t="n">
-        <v>7.28</v>
+        <v>6.37</v>
       </c>
       <c r="F21" t="n">
-        <v>9.07</v>
+        <v>5.25</v>
       </c>
       <c r="G21" t="n">
-        <v>-4</v>
+        <v>2.33</v>
       </c>
       <c r="H21" t="n">
-        <v>3.795</v>
+        <v>4.202500000000001</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1367,13 +1389,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L21" t="n">
-        <v>77.78</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="22">
@@ -1384,26 +1406,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>India Consumption Fund</t>
+          <t>Pension India Consumption Fund</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ULIF 158 170425 IndConsump 105</t>
+          <t>ULIF 159 190625 PenIndCons 105</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.86</v>
+        <v>2.82</v>
       </c>
       <c r="E22" t="n">
-        <v>3.05</v>
+        <v>6.22</v>
       </c>
       <c r="F22" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
+        <v>4.91</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.6</v>
+      </c>
       <c r="H22" t="n">
-        <v>1.68</v>
+        <v>3.8875</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1411,13 +1435,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L22" t="n">
-        <v>51.85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23">
@@ -1428,26 +1452,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pension India Consumption Fund</t>
+          <t>BSE 500 Enhanced Value 50 Index Fund</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ULIF 159 190625 PenIndCons 105</t>
+          <t>ULIF 161 091025 EnhancedVF 105</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.73</v>
+        <v>0.11</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.17</v>
-      </c>
+        <v>-2.04</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1.486666666666667</v>
+        <v>-0.965</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1455,13 +1477,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L23" t="n">
-        <v>44.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1472,26 +1494,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nifty Alpha 50 Index Fund</t>
+          <t>Sector Leaders Index Fund</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ULIF 160 290725 AlphaIndIF 105</t>
+          <t>ULIF 162 251125 SecLeaders 105</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.01</v>
+        <v>1.34</v>
       </c>
       <c r="E24" t="n">
-        <v>4.97</v>
+        <v>2.1</v>
       </c>
       <c r="F24" t="n">
-        <v>13.73</v>
+        <v>0.16</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>6.236666666666667</v>
+        <v>1.2</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1499,13 +1521,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>100</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="25">
@@ -1516,24 +1538,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BSE 500 Enhanced Value 50 Index Fund</t>
+          <t>Dividend Leaders 50 Index Fund</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ULIF 161 091025 EnhancedVF 105</t>
+          <t>ULIF 163 300126 DivLeaders 105</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-2.8</v>
+        <v>2.18</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.75</v>
+        <v>-3.21</v>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>-2.775</v>
+        <v>-0.5149999999999999</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1541,13 +1563,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>7.41</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="26">
@@ -1558,26 +1580,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sector Leaders Index Fund</t>
+          <t>Smallcap 250 Index Fund</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ULIF 162 251125 SecLeaders 105</t>
+          <t>ULIF 164 270226 Smallcp250 105</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.37</v>
+        <v>-0.72</v>
       </c>
       <c r="E26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.02</v>
-      </c>
+        <v>6.51</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.87</v>
+        <v>2.895</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1585,130 +1605,14 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>29.63</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ICICI Prudential</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Dividend Leaders 50 Index Fund</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ULIF 163 300126 DivLeaders 105</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-5.26</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>27</v>
-      </c>
-      <c r="K27" t="n">
-        <v>28</v>
-      </c>
-      <c r="L27" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ICICI Prudential</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Smallcap 250 Index Fund</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ULIF 164 270226 Smallcp250 105</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E28" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>5.925</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>28</v>
-      </c>
-      <c r="L28" t="n">
-        <v>96.3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ICICI Prudential</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Large N Mid Cap Advantage Fund</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ULIF 166 020626 LMidcapAdv 105</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>28</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>62.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
